--- a/LISTAS_ORDENADAS/MI/Soportes y escuadras/SOPORTE para CORTINA LIDIMA.xlsx
+++ b/LISTAS_ORDENADAS/MI/Soportes y escuadras/SOPORTE para CORTINA LIDIMA.xlsx
@@ -729,14 +729,10 @@
   <sheetData>
     <row r="1">
       <c r="A1" s="24" t="n">
-        <v>45154.58662823712</v>
+        <v>45266</v>
       </c>
       <c r="E1" s="6" t="n"/>
     </row>
-    <row r="2"/>
-    <row r="3"/>
-    <row r="4"/>
-    <row r="5"/>
     <row r="6" ht="22.5" customHeight="1" s="1">
       <c r="A6" s="2" t="inlineStr">
         <is>
@@ -782,22 +778,6 @@
       </c>
       <c r="E11" s="11" t="n"/>
     </row>
-    <row r="12"/>
-    <row r="13"/>
-    <row r="14"/>
-    <row r="15"/>
-    <row r="16"/>
-    <row r="17"/>
-    <row r="18"/>
-    <row r="19"/>
-    <row r="20"/>
-    <row r="21"/>
-    <row r="22"/>
-    <row r="23"/>
-    <row r="24"/>
-    <row r="25"/>
-    <row r="26"/>
-    <row r="27"/>
     <row r="28" ht="18" customHeight="1" s="1">
       <c r="A28" s="16" t="inlineStr">
         <is>
@@ -829,7 +809,7 @@
       </c>
       <c r="C29" s="27" t="n"/>
       <c r="D29" s="15" t="n">
-        <v>113.01</v>
+        <v>120</v>
       </c>
     </row>
     <row r="30" ht="19.5" customHeight="1" s="1">
@@ -893,7 +873,7 @@
       </c>
       <c r="C33" s="27" t="n"/>
       <c r="D33" s="15" t="n">
-        <v>117.5</v>
+        <v>140</v>
       </c>
     </row>
     <row r="34" ht="19.5" customHeight="1" s="1">
@@ -976,7 +956,6 @@
         <v>124.4</v>
       </c>
     </row>
-    <row r="39"/>
     <row r="40" ht="15" customHeight="1" s="1">
       <c r="A40" s="23" t="inlineStr">
         <is>
@@ -984,7 +963,6 @@
         </is>
       </c>
     </row>
-    <row r="41"/>
     <row r="42">
       <c r="A42" s="14" t="inlineStr">
         <is>
@@ -992,20 +970,12 @@
         </is>
       </c>
     </row>
-    <row r="43"/>
     <row r="44" ht="15" customHeight="1" s="1">
       <c r="A44" s="13" t="n"/>
     </row>
-    <row r="45"/>
     <row r="46">
       <c r="A46" s="14" t="n"/>
     </row>
-    <row r="47"/>
-    <row r="48"/>
-    <row r="49"/>
-    <row r="50"/>
-    <row r="51"/>
-    <row r="52"/>
     <row r="53" ht="15.75" customHeight="1" s="1">
       <c r="A53" s="4" t="n"/>
     </row>
@@ -1014,22 +984,22 @@
     </row>
   </sheetData>
   <mergeCells count="16">
+    <mergeCell ref="A1:D1"/>
     <mergeCell ref="A40:D40"/>
+    <mergeCell ref="B30:C30"/>
+    <mergeCell ref="A9:D9"/>
+    <mergeCell ref="B38:C38"/>
     <mergeCell ref="B29:C29"/>
-    <mergeCell ref="B30:C30"/>
-    <mergeCell ref="B31:C31"/>
-    <mergeCell ref="B32:C32"/>
     <mergeCell ref="B33:C33"/>
     <mergeCell ref="B34:C34"/>
+    <mergeCell ref="B37:C37"/>
     <mergeCell ref="B28:C28"/>
-    <mergeCell ref="B37:C37"/>
-    <mergeCell ref="B38:C38"/>
+    <mergeCell ref="B36:C36"/>
+    <mergeCell ref="B32:C32"/>
+    <mergeCell ref="B31:C31"/>
+    <mergeCell ref="A11:D11"/>
+    <mergeCell ref="A10:D10"/>
     <mergeCell ref="B35:C35"/>
-    <mergeCell ref="B36:C36"/>
-    <mergeCell ref="A1:D1"/>
-    <mergeCell ref="A9:D9"/>
-    <mergeCell ref="A10:D10"/>
-    <mergeCell ref="A11:D11"/>
   </mergeCells>
   <pageMargins left="0.7480314960629921" right="0.7480314960629921" top="0.984251968503937" bottom="0.984251968503937" header="0" footer="0"/>
   <pageSetup orientation="portrait" paperSize="5" horizontalDpi="0" verticalDpi="0"/>
